--- a/AAII_Financials/Yearly/BGAOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BGAOY_YR_FIN.xlsx
@@ -2184,7 +2184,7 @@
         <v>813500</v>
       </c>
       <c r="G58" s="3">
-        <v>706400</v>
+        <v>733100</v>
       </c>
       <c r="H58" s="3">
         <v>365100</v>
@@ -2217,7 +2217,7 @@
         <v>427800</v>
       </c>
       <c r="G59" s="3">
-        <v>347300</v>
+        <v>320600</v>
       </c>
       <c r="H59" s="3">
         <v>219500</v>
